--- a/SGC-CKN/Excel/10726635-509b-43c0-8e25-cf4301285f89_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P14-1_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/10726635-509b-43c0-8e25-cf4301285f89_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P14-1_D800_02-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -89,7 +89,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Đất lấp</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07:01
@@ -106,7 +109,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">07:15
@@ -116,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét- đổi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">21:03
@@ -130,7 +133,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét- đổi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">21:30
@@ -140,7 +143,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
     <t xml:space="preserve">22:50
@@ -150,7 +153,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">23:10
@@ -160,7 +163,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">02:20
@@ -168,16 +171,6 @@
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:12
-02/04/2026</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
@@ -221,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -287,18 +280,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF164E63"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -315,7 +303,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -344,17 +332,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -384,7 +367,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -394,7 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -490,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -525,82 +508,73 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -626,7 +600,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -986,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1177,328 +1151,294 @@
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-0.5</v>
+        <v>-2.1</v>
       </c>
       <c r="H11" s="5">
         <v>0.07</v>
       </c>
       <c r="I11" s="5">
-        <v>0.21</v>
+        <v>2.1</v>
       </c>
       <c r="J11" s="8">
-        <v>3.15</v>
+        <v>31.5</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-0.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G12" s="9">
-        <v>-2.1</v>
+        <v>-12.3</v>
       </c>
       <c r="H12" s="9">
         <v>0.17</v>
       </c>
       <c r="I12" s="9">
-        <v>1.6</v>
-      </c>
-      <c r="J12" s="12">
-        <v>9.6</v>
+        <v>10.2</v>
+      </c>
+      <c r="J12" s="8">
+        <v>61.2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
-        <v>-2.1</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="E13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="12">
         <v>-12.3</v>
       </c>
-      <c r="H13" s="13">
+      <c r="G13" s="12">
+        <v>-17.5</v>
+      </c>
+      <c r="H13" s="12">
         <v>0.12</v>
       </c>
-      <c r="I13" s="13">
-        <v>10.2</v>
-      </c>
-      <c r="J13" s="12">
-        <v>87.43</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>28</v>
+      <c r="I13" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>44.57</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="E14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="15">
+        <v>-17.5</v>
+      </c>
+      <c r="G14" s="15">
+        <v>-28.2</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0.33</v>
+      </c>
+      <c r="I14" s="15">
+        <v>10.7</v>
+      </c>
+      <c r="J14" s="8">
+        <v>32.1</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="16">
-        <v>-12.3</v>
-      </c>
-      <c r="G14" s="16">
-        <v>-17.5</v>
-      </c>
-      <c r="H14" s="16">
+      <c r="C15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="18">
+        <v>-28.2</v>
+      </c>
+      <c r="G15" s="18">
+        <v>-35</v>
+      </c>
+      <c r="H15" s="18">
+        <v>1.33</v>
+      </c>
+      <c r="I15" s="18">
+        <v>6.8</v>
+      </c>
+      <c r="J15" s="8">
+        <v>5.1</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="21">
+        <v>-35</v>
+      </c>
+      <c r="G16" s="21">
+        <v>-37.5</v>
+      </c>
+      <c r="H16" s="21">
         <v>0.33</v>
       </c>
-      <c r="I14" s="16">
-        <v>5.2</v>
-      </c>
-      <c r="J14" s="12">
-        <v>15.6</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="19" t="s">
+      <c r="I16" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="J16" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="19">
-        <v>-17.5</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-28.2</v>
-      </c>
-      <c r="H15" s="19">
-        <v>1.33</v>
-      </c>
-      <c r="I15" s="19">
-        <v>10.7</v>
-      </c>
-      <c r="J15" s="12">
-        <v>8.03</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="C17" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="24">
+        <v>-37.5</v>
+      </c>
+      <c r="G17" s="24">
+        <v>-44</v>
+      </c>
+      <c r="H17" s="24">
+        <v>3.17</v>
+      </c>
+      <c r="I17" s="24">
+        <v>6.5</v>
+      </c>
+      <c r="J17" s="27">
+        <v>2.05</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="22">
-        <v>-28.2</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-35</v>
-      </c>
-      <c r="H16" s="22">
-        <v>0.33</v>
-      </c>
-      <c r="I16" s="22">
-        <v>6.8</v>
-      </c>
-      <c r="J16" s="12">
-        <v>20.4</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="25">
-        <v>-35</v>
-      </c>
-      <c r="G17" s="25">
-        <v>-37.5</v>
-      </c>
-      <c r="H17" s="25">
-        <v>3.17</v>
-      </c>
-      <c r="I17" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="J17" s="28">
-        <v>0.79</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="29">
-        <v>-37.5</v>
-      </c>
-      <c r="G18" s="29">
+      <c r="E18" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="28">
         <v>-44</v>
       </c>
-      <c r="H18" s="29">
-        <v>1.87</v>
-      </c>
-      <c r="I18" s="29">
-        <v>6.5</v>
-      </c>
-      <c r="J18" s="8">
-        <v>3.48</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="33" t="s">
+      <c r="G18" s="28">
+        <v>-49.71</v>
+      </c>
+      <c r="H18" s="28">
+        <v>5905.87</v>
+      </c>
+      <c r="I18" s="28">
+        <v>5.71</v>
+      </c>
+      <c r="J18" s="31">
+        <v>0</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="32">
-        <v>-44</v>
-      </c>
-      <c r="G19" s="32">
-        <v>-49.71</v>
-      </c>
-      <c r="H19" s="32">
-        <v>1.87</v>
-      </c>
-      <c r="I19" s="32">
-        <v>5.71</v>
-      </c>
-      <c r="J19" s="8">
-        <v>3.06</v>
-      </c>
-      <c r="K19" s="33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-    </row>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1558,7 +1498,6 @@
     <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1569,7 +1508,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1579,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1592,31 +1531,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1627,25 +1566,25 @@
         <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-0.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G2" s="5">
         <v>0.07</v>
       </c>
       <c r="H2" s="5">
-        <v>0.21</v>
+        <v>2.1</v>
       </c>
       <c r="I2" s="8">
-        <v>3.15</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1656,257 +1595,228 @@
         <v>10</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-0.5</v>
+        <v>-2.1</v>
       </c>
       <c r="F3" s="9">
-        <v>-2.1</v>
+        <v>-12.3</v>
       </c>
       <c r="G3" s="9">
         <v>0.17</v>
       </c>
       <c r="H3" s="9">
-        <v>1.6</v>
-      </c>
-      <c r="I3" s="12">
-        <v>9.6</v>
+        <v>10.2</v>
+      </c>
+      <c r="I3" s="8">
+        <v>61.2</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-2.1</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
         <v>-12.3</v>
       </c>
-      <c r="G4" s="13">
+      <c r="F4" s="12">
+        <v>-17.5</v>
+      </c>
+      <c r="G4" s="12">
         <v>0.12</v>
       </c>
-      <c r="H4" s="13">
-        <v>10.2</v>
-      </c>
-      <c r="I4" s="12">
-        <v>87.43</v>
+      <c r="H4" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>44.57</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-12.3</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
         <v>-17.5</v>
       </c>
-      <c r="G5" s="16">
+      <c r="F5" s="15">
+        <v>-28.2</v>
+      </c>
+      <c r="G5" s="15">
         <v>0.33</v>
       </c>
-      <c r="H5" s="16">
-        <v>5.2</v>
-      </c>
-      <c r="I5" s="12">
-        <v>15.6</v>
+      <c r="H5" s="15">
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="8">
+        <v>32.1</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C6" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-17.5</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="E6" s="18">
         <v>-28.2</v>
       </c>
-      <c r="G6" s="19">
+      <c r="F6" s="18">
+        <v>-35</v>
+      </c>
+      <c r="G6" s="18">
         <v>1.33</v>
       </c>
-      <c r="H6" s="19">
-        <v>10.7</v>
-      </c>
-      <c r="I6" s="12">
-        <v>8.03</v>
+      <c r="H6" s="18">
+        <v>6.8</v>
+      </c>
+      <c r="I6" s="8">
+        <v>5.1</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C7" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
-        <v>-28.2</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E7" s="21">
         <v>-35</v>
       </c>
-      <c r="G7" s="22">
+      <c r="F7" s="21">
+        <v>-37.5</v>
+      </c>
+      <c r="G7" s="21">
         <v>0.33</v>
       </c>
-      <c r="H7" s="22">
-        <v>6.8</v>
-      </c>
-      <c r="I7" s="12">
-        <v>20.4</v>
+      <c r="H7" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="8">
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="C8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
-        <v>-35</v>
-      </c>
-      <c r="F8" s="25">
+      <c r="E8" s="24">
         <v>-37.5</v>
       </c>
-      <c r="G8" s="25">
+      <c r="F8" s="24">
+        <v>-44</v>
+      </c>
+      <c r="G8" s="24">
         <v>3.17</v>
       </c>
-      <c r="H8" s="25">
-        <v>2.5</v>
-      </c>
-      <c r="I8" s="28">
-        <v>0.79</v>
+      <c r="H8" s="24">
+        <v>6.5</v>
+      </c>
+      <c r="I8" s="27">
+        <v>2.05</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="C9" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
-        <v>-37.5</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="E9" s="28">
         <v>-44</v>
       </c>
-      <c r="G9" s="29">
-        <v>1.87</v>
-      </c>
-      <c r="H9" s="29">
-        <v>6.5</v>
-      </c>
-      <c r="I9" s="8">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
-        <v>9</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="32">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32">
-        <v>-44</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="F9" s="28">
         <v>-49.71</v>
       </c>
-      <c r="G10" s="32">
-        <v>1.87</v>
-      </c>
-      <c r="H10" s="32">
+      <c r="G9" s="28">
+        <v>5905.87</v>
+      </c>
+      <c r="H9" s="28">
         <v>5.71</v>
       </c>
-      <c r="I10" s="8">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="37">
-        <v>9</v>
-      </c>
-      <c r="E11" s="37">
-        <v>-0.71</v>
-      </c>
-      <c r="F11" s="37">
+      <c r="I9" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="34">
+        <v>8</v>
+      </c>
+      <c r="E10" s="34">
+        <v>0</v>
+      </c>
+      <c r="F10" s="34">
         <v>-49.71</v>
       </c>
-      <c r="G11" s="37">
-        <v>9.25</v>
-      </c>
-      <c r="H11" s="37">
-        <v>49.42</v>
-      </c>
-      <c r="I11" s="37">
-        <v>5.34</v>
+      <c r="G10" s="34">
+        <v>5911.38</v>
+      </c>
+      <c r="H10" s="34">
+        <v>49.71</v>
+      </c>
+      <c r="I10" s="34">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/10726635-509b-43c0-8e25-cf4301285f89_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P14-1_D800_02-04-2026.xlsx
+++ b/SGC-CKN/Excel/10726635-509b-43c0-8e25-cf4301285f89_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P14-1_D800_02-04-2026.xlsx
@@ -177,7 +177,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:12
-04/12/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -214,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -287,12 +287,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -303,7 +297,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -373,11 +367,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -473,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -565,16 +554,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1411,32 +1397,32 @@
         <v>-49.71</v>
       </c>
       <c r="H18" s="28">
-        <v>5905.87</v>
+        <v>1.87</v>
       </c>
       <c r="I18" s="28">
         <v>5.71</v>
       </c>
-      <c r="J18" s="31">
-        <v>0</v>
+      <c r="J18" s="27">
+        <v>3.06</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1781,42 +1767,42 @@
         <v>-49.71</v>
       </c>
       <c r="G9" s="28">
-        <v>5905.87</v>
+        <v>1.87</v>
       </c>
       <c r="H9" s="28">
         <v>5.71</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="27">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="33">
+        <v>8</v>
+      </c>
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="34">
-        <v>8</v>
-      </c>
-      <c r="E10" s="34">
-        <v>0</v>
-      </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-49.71</v>
       </c>
-      <c r="G10" s="34">
-        <v>5911.38</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="33">
+        <v>7.38</v>
+      </c>
+      <c r="H10" s="33">
         <v>49.71</v>
       </c>
-      <c r="I10" s="34">
-        <v>0.01</v>
+      <c r="I10" s="33">
+        <v>6.73</v>
       </c>
     </row>
   </sheetData>
